--- a/originales/respuestas/2025/01. Calificadas/bucle p11/Secretaría Distrital De Movilidad.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p11/Secretaría Distrital De Movilidad.xlsx
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+  <si>
+    <t>Entidad</t>
+  </si>
   <si>
     <t>Tipo</t>
   </si>
@@ -258,7 +261,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -495,101 +498,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4">
         <v>1.20171959E9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4">
         <v>5.0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4">
         <v>5.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="4">
         <v>5.0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="4">
         <v>5.0</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="4">
         <v>5.0</v>
@@ -598,49 +603,49 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4">
         <v>4.33323976E9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4">
         <v>5.0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="4">
         <v>5.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="4">
         <v>5.0</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" s="4">
         <v>5.0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="4">
         <v>5.0</v>
@@ -649,47 +654,47 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="4">
         <v>0.0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="5">
         <v>1.0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="5">
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="4">
         <v>5.0</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" s="5">
         <v>1.0</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="4">
         <v>5.0</v>
@@ -698,47 +703,47 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4">
         <v>1.378722381E9</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="5">
         <v>1.0</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4">
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="4">
         <v>5.0</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5" s="4">
         <v>5.0</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="4">
         <v>5.0</v>
@@ -747,47 +752,47 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4">
         <v>2.2950459E8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="5">
         <v>1.0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="4">
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="4">
         <v>5.0</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N6" s="4">
         <v>5.0</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="4">
         <v>5.0</v>
@@ -796,47 +801,47 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="4">
         <v>3.47996593E8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="5">
         <v>1.0</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4">
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4">
         <v>5.0</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N7" s="4">
         <v>5.0</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="4">
         <v>5.0</v>
@@ -845,41 +850,41 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="5">
         <v>1.0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="5">
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="5">
         <v>1.0</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="5">
         <v>1.0</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" s="4">
         <v>5.0</v>
@@ -888,41 +893,41 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="5">
         <v>1.0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="5">
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="5">
         <v>1.0</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N9" s="5">
         <v>1.0</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" s="4">
         <v>5.0</v>
@@ -931,41 +936,41 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="5">
         <v>1.0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="5">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="5">
         <v>1.0</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" s="5">
         <v>1.0</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P10" s="4">
         <v>5.0</v>
